--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="G2">
-        <v>400</v>
+        <v>176</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>118</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="G3">
-        <v>409</v>
+        <v>172</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.1-8B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D2">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E2">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="D3">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E3">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G3">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="H3">
         <v>426</v>
